--- a/sampleprojects/CorporateTax/excel/CorporateTax_map.xlsx
+++ b/sampleprojects/CorporateTax/excel/CorporateTax_map.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="364">
   <si>
     <t>MAP: CorporateTax</t>
   </si>
@@ -394,15 +394,144 @@
 			     absent — they belong to the state's law and stay as EDD defaults.</t>
   </si>
   <si>
+    <t>federal_tax_liability</t>
+  </si>
+  <si>
+    <t>has_physical_presence_co</t>
+  </si>
+  <si>
+    <t>has_physical_presence_ia</t>
+  </si>
+  <si>
+    <t>has_physical_presence_id</t>
+  </si>
+  <si>
+    <t>has_physical_presence_in</t>
+  </si>
+  <si>
+    <t>has_physical_presence_ks</t>
+  </si>
+  <si>
+    <t>has_physical_presence_ky</t>
+  </si>
+  <si>
+    <t>has_physical_presence_la</t>
+  </si>
+  <si>
+    <t>has_physical_presence_ma</t>
+  </si>
+  <si>
+    <t>has_physical_presence_md</t>
+  </si>
+  <si>
+    <t>has_physical_presence_me</t>
+  </si>
+  <si>
+    <t>has_physical_presence_mi</t>
+  </si>
+  <si>
+    <t>has_physical_presence_mn</t>
+  </si>
+  <si>
+    <t>has_physical_presence_mo</t>
+  </si>
+  <si>
+    <t>has_physical_presence_ms</t>
+  </si>
+  <si>
+    <t>has_physical_presence_mt</t>
+  </si>
+  <si>
+    <t>has_physical_presence_nv</t>
+  </si>
+  <si>
+    <t>section_199a_deduction</t>
+  </si>
+  <si>
+    <t>state_income_taxes_paid</t>
+  </si>
+  <si>
+    <t>total_revenue</t>
+  </si>
+  <si>
+    <t># Job entity</t>
+  </si>
+  <si>
+    <t># Corporation entity</t>
+  </si>
+  <si>
+    <t># Revenue entity</t>
+  </si>
+  <si>
+    <t># Expense entity</t>
+  </si>
+  <si>
+    <t># Asset entity</t>
+  </si>
+  <si>
+    <t># Result entity</t>
+  </si>
+  <si>
+    <t>me_apportioned_income</t>
+  </si>
+  <si>
+    <t>apportioned_income</t>
+  </si>
+  <si>
+    <t>me_result</t>
+  </si>
+  <si>
+    <t>me_estimated_payments</t>
+  </si>
+  <si>
+    <t>estimated_payments</t>
+  </si>
+  <si>
+    <t>me_gross_receipts</t>
+  </si>
+  <si>
+    <t>me_municipal_interest</t>
+  </si>
+  <si>
+    <t>municipal_interest</t>
+  </si>
+  <si>
+    <t>me_section_199a_addback</t>
+  </si>
+  <si>
+    <t>section_199a_addback</t>
+  </si>
+  <si>
+    <t>me_state_credits</t>
+  </si>
+  <si>
+    <t>me_us_interest_income</t>
+  </si>
+  <si>
+    <t>us_interest_income</t>
+  </si>
+  <si>
     <t>ca_unitary_group_count</t>
   </si>
   <si>
+    <t>unitary_group_count</t>
+  </si>
+  <si>
+    <t>ca_result</t>
+  </si>
+  <si>
     <t>ca_waters_edge_election</t>
   </si>
   <si>
+    <t>waters_edge_election</t>
+  </si>
+  <si>
     <t>co_apportioned_income</t>
   </si>
   <si>
+    <t>co_result</t>
+  </si>
+  <si>
     <t>co_estimated_payments</t>
   </si>
   <si>
@@ -415,66 +544,24 @@
     <t>co_state_tax_deduction</t>
   </si>
   <si>
+    <t>state_tax_deduction</t>
+  </si>
+  <si>
     <t>co_us_interest_income</t>
   </si>
   <si>
     <t>dc_gross_receipts</t>
   </si>
   <si>
-    <t>federal_tax_liability</t>
-  </si>
-  <si>
-    <t>has_physical_presence_co</t>
-  </si>
-  <si>
-    <t>has_physical_presence_ia</t>
-  </si>
-  <si>
-    <t>has_physical_presence_id</t>
-  </si>
-  <si>
-    <t>has_physical_presence_in</t>
-  </si>
-  <si>
-    <t>has_physical_presence_ks</t>
-  </si>
-  <si>
-    <t>has_physical_presence_ky</t>
-  </si>
-  <si>
-    <t>has_physical_presence_la</t>
-  </si>
-  <si>
-    <t>has_physical_presence_ma</t>
-  </si>
-  <si>
-    <t>has_physical_presence_md</t>
-  </si>
-  <si>
-    <t>has_physical_presence_me</t>
-  </si>
-  <si>
-    <t>has_physical_presence_mi</t>
-  </si>
-  <si>
-    <t>has_physical_presence_mn</t>
-  </si>
-  <si>
-    <t>has_physical_presence_mo</t>
-  </si>
-  <si>
-    <t>has_physical_presence_ms</t>
-  </si>
-  <si>
-    <t>has_physical_presence_mt</t>
-  </si>
-  <si>
-    <t>has_physical_presence_nv</t>
+    <t>dc_result</t>
   </si>
   <si>
     <t>ia_apportioned_income</t>
   </si>
   <si>
+    <t>ia_result</t>
+  </si>
+  <si>
     <t>ia_estimated_payments</t>
   </si>
   <si>
@@ -490,12 +577,18 @@
     <t>ia_state_taxes_deducted</t>
   </si>
   <si>
+    <t>state_taxes_deducted</t>
+  </si>
+  <si>
     <t>ia_us_interest_income</t>
   </si>
   <si>
     <t>id_apportioned_income</t>
   </si>
   <si>
+    <t>id_result</t>
+  </si>
+  <si>
     <t>id_estimated_payments</t>
   </si>
   <si>
@@ -517,6 +610,9 @@
     <t>in_apportioned_income</t>
   </si>
   <si>
+    <t>in_result</t>
+  </si>
+  <si>
     <t>in_estimated_payments</t>
   </si>
   <si>
@@ -529,15 +625,24 @@
     <t>in_out_of_state_muni_interest</t>
   </si>
   <si>
+    <t>out_of_state_muni_interest</t>
+  </si>
+  <si>
     <t>in_state_credits</t>
   </si>
   <si>
     <t>in_state_taxes_paid</t>
   </si>
   <si>
+    <t>state_taxes_paid</t>
+  </si>
+  <si>
     <t>ks_apportioned_income</t>
   </si>
   <si>
+    <t>ks_result</t>
+  </si>
+  <si>
     <t>ks_estimated_payments</t>
   </si>
   <si>
@@ -553,6 +658,9 @@
     <t>ks_state_tax_refunds</t>
   </si>
   <si>
+    <t>state_tax_refunds</t>
+  </si>
+  <si>
     <t>ks_state_taxes_paid</t>
   </si>
   <si>
@@ -562,9 +670,15 @@
     <t>ky_apportioned_income</t>
   </si>
   <si>
+    <t>ky_result</t>
+  </si>
+  <si>
     <t>ky_dividends_from_ky_corps</t>
   </si>
   <si>
+    <t>dividends_from_ky_corps</t>
+  </si>
+  <si>
     <t>ky_estimated_payments</t>
   </si>
   <si>
@@ -583,6 +697,9 @@
     <t>la_apportioned_income</t>
   </si>
   <si>
+    <t>la_result</t>
+  </si>
+  <si>
     <t>la_estimated_payments</t>
   </si>
   <si>
@@ -601,6 +718,9 @@
     <t>ma_apportioned_income</t>
   </si>
   <si>
+    <t>ma_result</t>
+  </si>
+  <si>
     <t>ma_estimated_payments</t>
   </si>
   <si>
@@ -613,6 +733,9 @@
     <t>ma_qualified_dividend_deduction</t>
   </si>
   <si>
+    <t>qualified_dividend_deduction</t>
+  </si>
+  <si>
     <t>ma_state_credits</t>
   </si>
   <si>
@@ -622,6 +745,9 @@
     <t>md_apportioned_income</t>
   </si>
   <si>
+    <t>md_result</t>
+  </si>
+  <si>
     <t>md_estimated_payments</t>
   </si>
   <si>
@@ -637,30 +763,12 @@
     <t>md_us_interest_income</t>
   </si>
   <si>
-    <t>me_apportioned_income</t>
-  </si>
-  <si>
-    <t>me_estimated_payments</t>
-  </si>
-  <si>
-    <t>me_gross_receipts</t>
-  </si>
-  <si>
-    <t>me_municipal_interest</t>
-  </si>
-  <si>
-    <t>me_section_199a_addback</t>
-  </si>
-  <si>
-    <t>me_state_credits</t>
-  </si>
-  <si>
-    <t>me_us_interest_income</t>
-  </si>
-  <si>
     <t>mi_apportioned_income</t>
   </si>
   <si>
+    <t>mi_result</t>
+  </si>
+  <si>
     <t>mi_estimated_payments</t>
   </si>
   <si>
@@ -679,6 +787,9 @@
     <t>mn_apportioned_income</t>
   </si>
   <si>
+    <t>mn_result</t>
+  </si>
+  <si>
     <t>mn_estimated_payments</t>
   </si>
   <si>
@@ -697,6 +808,9 @@
     <t>mo_apportioned_income</t>
   </si>
   <si>
+    <t>mo_result</t>
+  </si>
+  <si>
     <t>mo_estimated_payments</t>
   </si>
   <si>
@@ -715,6 +829,9 @@
     <t>ms_apportioned_income</t>
   </si>
   <si>
+    <t>ms_result</t>
+  </si>
+  <si>
     <t>ms_estimated_payments</t>
   </si>
   <si>
@@ -733,6 +850,9 @@
     <t>mt_apportioned_income</t>
   </si>
   <si>
+    <t>mt_result</t>
+  </si>
+  <si>
     <t>mt_estimated_payments</t>
   </si>
   <si>
@@ -754,70 +874,235 @@
     <t>nv_business_classification</t>
   </si>
   <si>
+    <t>business_classification</t>
+  </si>
+  <si>
+    <t>nv_result</t>
+  </si>
+  <si>
     <t>ny_in_mta_region</t>
   </si>
   <si>
+    <t>in_mta_region</t>
+  </si>
+  <si>
+    <t>ny_result</t>
+  </si>
+  <si>
     <t>or_is_financial_institution</t>
   </si>
   <si>
+    <t>is_financial_institution</t>
+  </si>
+  <si>
+    <t>or_result</t>
+  </si>
+  <si>
     <t>sd_is_financial_institution</t>
   </si>
   <si>
+    <t>sd_result</t>
+  </si>
+  <si>
     <t>sd_is_insurance_company</t>
   </si>
   <si>
-    <t>section_199a_deduction</t>
-  </si>
-  <si>
-    <t>state_income_taxes_paid</t>
+    <t>is_insurance_company</t>
   </si>
   <si>
     <t>tn_net_worth</t>
   </si>
   <si>
+    <t>net_worth</t>
+  </si>
+  <si>
+    <t>tn_result</t>
+  </si>
+  <si>
     <t>tn_nol_deduction</t>
   </si>
   <si>
-    <t>total_revenue</t>
+    <t>nol_deduction</t>
   </si>
   <si>
     <t>tx_cogs</t>
   </si>
   <si>
+    <t>cogs</t>
+  </si>
+  <si>
+    <t>tx_result</t>
+  </si>
+  <si>
     <t>tx_compensation</t>
   </si>
   <si>
     <t>tx_is_retail_wholesale</t>
   </si>
   <si>
+    <t>is_retail_wholesale</t>
+  </si>
+  <si>
     <t>tx_total_revenue</t>
   </si>
   <si>
     <t>wa_business_classification</t>
   </si>
   <si>
-    <t># Job entity</t>
-  </si>
-  <si>
-    <t># Corporation entity</t>
-  </si>
-  <si>
-    <t># Revenue entity</t>
-  </si>
-  <si>
-    <t># Expense entity</t>
-  </si>
-  <si>
-    <t># Asset entity</t>
-  </si>
-  <si>
-    <t># Result entity</t>
+    <t>wa_result</t>
   </si>
   <si>
     <t>## CREATE ENTITIES (entity | tag | id | list)</t>
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>ak_apportionment</t>
+  </si>
+  <si>
+    <t>al_apportionment</t>
+  </si>
+  <si>
+    <t>ar_apportionment</t>
+  </si>
+  <si>
+    <t>az_apportionment</t>
+  </si>
+  <si>
+    <t>ca_apportionment</t>
+  </si>
+  <si>
+    <t>ct_apportionment</t>
+  </si>
+  <si>
+    <t>dc_apportionment</t>
+  </si>
+  <si>
+    <t>de_apportionment</t>
+  </si>
+  <si>
+    <t>fl_apportionment</t>
+  </si>
+  <si>
+    <t>ga_apportionment</t>
+  </si>
+  <si>
+    <t>hi_apportionment</t>
+  </si>
+  <si>
+    <t>il_apportionment</t>
+  </si>
+  <si>
+    <t>il_result</t>
+  </si>
+  <si>
+    <t>ma_apportionment</t>
+  </si>
+  <si>
+    <t>me_apportionment</t>
+  </si>
+  <si>
+    <t>mi_apportionment</t>
+  </si>
+  <si>
+    <t>mn_apportionment</t>
+  </si>
+  <si>
+    <t>mo_apportionment</t>
+  </si>
+  <si>
+    <t>ms_apportionment</t>
+  </si>
+  <si>
+    <t>mt_apportionment</t>
+  </si>
+  <si>
+    <t>nc_apportionment</t>
+  </si>
+  <si>
+    <t>nd_apportionment</t>
+  </si>
+  <si>
+    <t>ne_apportionment</t>
+  </si>
+  <si>
+    <t>nh_apportionment</t>
+  </si>
+  <si>
+    <t>nh_result</t>
+  </si>
+  <si>
+    <t>nj_apportionment</t>
+  </si>
+  <si>
+    <t>nj_result</t>
+  </si>
+  <si>
+    <t>nm_apportionment</t>
+  </si>
+  <si>
+    <t>nv_apportionment</t>
+  </si>
+  <si>
+    <t>ny_apportionment</t>
+  </si>
+  <si>
+    <t>oh_apportionment</t>
+  </si>
+  <si>
+    <t>oh_result</t>
+  </si>
+  <si>
+    <t>ok_apportionment</t>
+  </si>
+  <si>
+    <t>or_apportionment</t>
+  </si>
+  <si>
+    <t>pa_apportionment</t>
+  </si>
+  <si>
+    <t>ri_apportionment</t>
+  </si>
+  <si>
+    <t>sc_apportionment</t>
+  </si>
+  <si>
+    <t>sd_apportionment</t>
+  </si>
+  <si>
+    <t>tn_apportionment</t>
+  </si>
+  <si>
+    <t>tn_revenue</t>
+  </si>
+  <si>
+    <t>tx_apportionment</t>
+  </si>
+  <si>
+    <t>ut_apportionment</t>
+  </si>
+  <si>
+    <t>va_apportionment</t>
+  </si>
+  <si>
+    <t>vt_apportionment</t>
+  </si>
+  <si>
+    <t>wa_apportionment</t>
+  </si>
+  <si>
+    <t>wi_apportionment</t>
+  </si>
+  <si>
+    <t>wv_apportionment</t>
+  </si>
+  <si>
+    <t>wy_apportionment</t>
+  </si>
+  <si>
+    <t>wy_result</t>
   </si>
   <si>
     <t>## ENTITIES (name | number: 1 or *)</t>
@@ -2691,7 +2976,7 @@
         <v>70</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="114">
@@ -2719,7 +3004,7 @@
         <v>70</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
     </row>
     <row r="116">
@@ -2733,7 +3018,7 @@
         <v>70</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
     </row>
     <row r="117">
@@ -2747,7 +3032,7 @@
         <v>70</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
     </row>
     <row r="118">
@@ -2761,7 +3046,7 @@
         <v>70</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
     </row>
     <row r="119">
@@ -2775,7 +3060,7 @@
         <v>70</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
     </row>
     <row r="120">
@@ -2789,7 +3074,7 @@
         <v>70</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
     </row>
     <row r="121">
@@ -2803,7 +3088,7 @@
         <v>70</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
     </row>
     <row r="122">
@@ -2817,7 +3102,7 @@
         <v>70</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
     </row>
     <row r="123">
@@ -2929,7 +3214,7 @@
         <v>70</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
     </row>
     <row r="131">
@@ -2943,7 +3228,7 @@
         <v>70</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
     </row>
     <row r="132">
@@ -2957,200 +3242,188 @@
         <v>70</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="s">
+      <c r="A133" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="B133" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>49</v>
-      </c>
+      <c r="B133" s="6"/>
+      <c r="C133" s="6"/>
+      <c r="D133" s="6"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>144</v>
+        <v>6</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>144</v>
+        <v>6</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>145</v>
+        <v>9</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>145</v>
+        <v>9</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>146</v>
+        <v>11</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>146</v>
+        <v>11</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>147</v>
+        <v>13</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>147</v>
+        <v>13</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>148</v>
+        <v>14</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>148</v>
+        <v>14</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B139" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D139" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="A139" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B139" s="6"/>
+      <c r="C139" s="6"/>
+      <c r="D139" s="6"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>150</v>
+        <v>21</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>150</v>
+        <v>21</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>151</v>
+        <v>23</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>151</v>
+        <v>23</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>152</v>
+        <v>24</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>152</v>
+        <v>24</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>153</v>
+        <v>25</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>153</v>
+        <v>25</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>154</v>
+        <v>26</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>154</v>
+        <v>26</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>155</v>
+        <v>27</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>155</v>
+        <v>27</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>156</v>
+        <v>28</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>156</v>
+        <v>28</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>17</v>
@@ -3158,41 +3431,35 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>157</v>
+        <v>29</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>157</v>
+        <v>29</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D148" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="A148" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B148" s="6"/>
+      <c r="C148" s="6"/>
+      <c r="D148" s="6"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>159</v>
+        <v>29</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>159</v>
+        <v>29</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>17</v>
@@ -3200,13 +3467,13 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>160</v>
+        <v>32</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>160</v>
+        <v>32</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>17</v>
@@ -3214,13 +3481,13 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>161</v>
+        <v>33</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>161</v>
+        <v>33</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>17</v>
@@ -3228,13 +3495,13 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>162</v>
+        <v>34</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>162</v>
+        <v>34</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>17</v>
@@ -3242,13 +3509,13 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>163</v>
+        <v>35</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>163</v>
+        <v>35</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>17</v>
@@ -3256,13 +3523,13 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>164</v>
+        <v>36</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>164</v>
+        <v>36</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>17</v>
@@ -3270,13 +3537,13 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>165</v>
+        <v>37</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>165</v>
+        <v>37</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>17</v>
@@ -3284,13 +3551,13 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>166</v>
+        <v>38</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>166</v>
+        <v>38</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>17</v>
@@ -3298,13 +3565,13 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>167</v>
+        <v>39</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>167</v>
+        <v>39</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>17</v>
@@ -3312,13 +3579,13 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>168</v>
+        <v>40</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>168</v>
+        <v>40</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>17</v>
@@ -3326,13 +3593,13 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>169</v>
+        <v>41</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>169</v>
+        <v>41</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>17</v>
@@ -3340,13 +3607,13 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>170</v>
+        <v>42</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>170</v>
+        <v>42</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>17</v>
@@ -3354,69 +3621,63 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>171</v>
+        <v>43</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>171</v>
+        <v>43</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B162" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C162" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D162" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="A162" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B162" s="6"/>
+      <c r="C162" s="6"/>
+      <c r="D162" s="6"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
-        <v>173</v>
+        <v>6</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>173</v>
+        <v>6</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>174</v>
+        <v>46</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>174</v>
+        <v>46</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
-        <v>175</v>
+        <v>47</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>175</v>
+        <v>47</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>17</v>
@@ -3424,97 +3685,91 @@
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
-        <v>176</v>
+        <v>48</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>176</v>
+        <v>48</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
-        <v>177</v>
+        <v>50</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>177</v>
+        <v>50</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="B168" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C168" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D168" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="A168" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B168" s="6"/>
+      <c r="C168" s="6"/>
+      <c r="D168" s="6"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="s">
-        <v>179</v>
+        <v>6</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>179</v>
+        <v>6</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
-        <v>180</v>
+        <v>53</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>180</v>
+        <v>53</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
-        <v>181</v>
+        <v>54</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>181</v>
+        <v>54</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
-        <v>182</v>
+        <v>55</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>182</v>
+        <v>55</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>17</v>
@@ -3522,69 +3777,69 @@
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
-        <v>183</v>
+        <v>56</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>183</v>
+        <v>56</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
-        <v>184</v>
+        <v>57</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>184</v>
+        <v>57</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
-        <v>185</v>
+        <v>58</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>185</v>
+        <v>58</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="s">
-        <v>186</v>
+        <v>59</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>186</v>
+        <v>59</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="s">
-        <v>187</v>
+        <v>60</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>187</v>
+        <v>60</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>17</v>
@@ -3592,13 +3847,13 @@
     </row>
     <row r="178">
       <c r="A178" s="2" t="s">
-        <v>188</v>
+        <v>61</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>188</v>
+        <v>61</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>17</v>
@@ -3606,13 +3861,13 @@
     </row>
     <row r="179">
       <c r="A179" s="2" t="s">
-        <v>189</v>
+        <v>62</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>189</v>
+        <v>62</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>17</v>
@@ -3620,13 +3875,13 @@
     </row>
     <row r="180">
       <c r="A180" s="2" t="s">
-        <v>190</v>
+        <v>63</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>190</v>
+        <v>63</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>17</v>
@@ -3634,80 +3889,74 @@
     </row>
     <row r="181">
       <c r="A181" s="2" t="s">
-        <v>191</v>
+        <v>64</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>191</v>
+        <v>64</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="s">
-        <v>192</v>
+        <v>65</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>192</v>
+        <v>65</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="s">
-        <v>193</v>
+        <v>66</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>193</v>
+        <v>66</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="s">
-        <v>194</v>
+        <v>67</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>194</v>
+        <v>67</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="B185" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C185" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D185" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="A185" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B185" s="6"/>
+      <c r="C185" s="6"/>
+      <c r="D185" s="6"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="s">
-        <v>196</v>
+        <v>43</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>196</v>
+        <v>43</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>70</v>
@@ -3718,10 +3967,10 @@
     </row>
     <row r="187">
       <c r="A187" s="2" t="s">
-        <v>197</v>
+        <v>72</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>197</v>
+        <v>72</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>70</v>
@@ -3732,10 +3981,10 @@
     </row>
     <row r="188">
       <c r="A188" s="2" t="s">
-        <v>198</v>
+        <v>73</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>198</v>
+        <v>73</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>70</v>
@@ -3746,10 +3995,10 @@
     </row>
     <row r="189">
       <c r="A189" s="2" t="s">
-        <v>199</v>
+        <v>74</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>199</v>
+        <v>74</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>70</v>
@@ -3760,10 +4009,10 @@
     </row>
     <row r="190">
       <c r="A190" s="2" t="s">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>70</v>
@@ -3774,10 +4023,10 @@
     </row>
     <row r="191">
       <c r="A191" s="2" t="s">
-        <v>201</v>
+        <v>76</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>201</v>
+        <v>76</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>70</v>
@@ -3788,10 +4037,10 @@
     </row>
     <row r="192">
       <c r="A192" s="2" t="s">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>70</v>
@@ -3802,10 +4051,10 @@
     </row>
     <row r="193">
       <c r="A193" s="2" t="s">
-        <v>203</v>
+        <v>78</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>203</v>
+        <v>78</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>70</v>
@@ -3816,10 +4065,10 @@
     </row>
     <row r="194">
       <c r="A194" s="2" t="s">
-        <v>204</v>
+        <v>79</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>204</v>
+        <v>79</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>70</v>
@@ -3830,10 +4079,10 @@
     </row>
     <row r="195">
       <c r="A195" s="2" t="s">
-        <v>205</v>
+        <v>80</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>205</v>
+        <v>80</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>70</v>
@@ -3844,10 +4093,10 @@
     </row>
     <row r="196">
       <c r="A196" s="2" t="s">
-        <v>206</v>
+        <v>81</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>206</v>
+        <v>81</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>70</v>
@@ -3858,10 +4107,10 @@
     </row>
     <row r="197">
       <c r="A197" s="2" t="s">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>70</v>
@@ -3872,10 +4121,10 @@
     </row>
     <row r="198">
       <c r="A198" s="2" t="s">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>70</v>
@@ -3886,10 +4135,10 @@
     </row>
     <row r="199">
       <c r="A199" s="2" t="s">
-        <v>209</v>
+        <v>84</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>209</v>
+        <v>84</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>70</v>
@@ -3900,10 +4149,10 @@
     </row>
     <row r="200">
       <c r="A200" s="2" t="s">
-        <v>210</v>
+        <v>85</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>210</v>
+        <v>85</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>70</v>
@@ -3914,10 +4163,10 @@
     </row>
     <row r="201">
       <c r="A201" s="2" t="s">
-        <v>211</v>
+        <v>86</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>211</v>
+        <v>86</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>70</v>
@@ -3928,10 +4177,10 @@
     </row>
     <row r="202">
       <c r="A202" s="2" t="s">
-        <v>212</v>
+        <v>88</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>212</v>
+        <v>88</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>70</v>
@@ -3942,10 +4191,10 @@
     </row>
     <row r="203">
       <c r="A203" s="2" t="s">
-        <v>213</v>
+        <v>89</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>213</v>
+        <v>89</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>70</v>
@@ -3956,10 +4205,10 @@
     </row>
     <row r="204">
       <c r="A204" s="2" t="s">
-        <v>214</v>
+        <v>90</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>214</v>
+        <v>90</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>70</v>
@@ -3970,10 +4219,10 @@
     </row>
     <row r="205">
       <c r="A205" s="2" t="s">
-        <v>215</v>
+        <v>91</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>215</v>
+        <v>91</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>70</v>
@@ -3984,10 +4233,10 @@
     </row>
     <row r="206">
       <c r="A206" s="2" t="s">
-        <v>216</v>
+        <v>92</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>216</v>
+        <v>92</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>70</v>
@@ -3998,10 +4247,10 @@
     </row>
     <row r="207">
       <c r="A207" s="2" t="s">
-        <v>217</v>
+        <v>93</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>217</v>
+        <v>93</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>70</v>
@@ -4012,10 +4261,10 @@
     </row>
     <row r="208">
       <c r="A208" s="2" t="s">
-        <v>218</v>
+        <v>95</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>218</v>
+        <v>95</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>70</v>
@@ -4026,10 +4275,10 @@
     </row>
     <row r="209">
       <c r="A209" s="2" t="s">
-        <v>219</v>
+        <v>96</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>219</v>
+        <v>96</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>70</v>
@@ -4040,10 +4289,10 @@
     </row>
     <row r="210">
       <c r="A210" s="2" t="s">
-        <v>220</v>
+        <v>97</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>220</v>
+        <v>97</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>70</v>
@@ -4054,10 +4303,10 @@
     </row>
     <row r="211">
       <c r="A211" s="2" t="s">
-        <v>221</v>
+        <v>99</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>221</v>
+        <v>99</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>70</v>
@@ -4068,10 +4317,10 @@
     </row>
     <row r="212">
       <c r="A212" s="2" t="s">
-        <v>222</v>
+        <v>100</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>222</v>
+        <v>100</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>70</v>
@@ -4082,10 +4331,10 @@
     </row>
     <row r="213">
       <c r="A213" s="2" t="s">
-        <v>223</v>
+        <v>101</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>223</v>
+        <v>101</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>70</v>
@@ -4096,10 +4345,10 @@
     </row>
     <row r="214">
       <c r="A214" s="2" t="s">
-        <v>224</v>
+        <v>102</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>224</v>
+        <v>102</v>
       </c>
       <c r="C214" s="2" t="s">
         <v>70</v>
@@ -4110,10 +4359,10 @@
     </row>
     <row r="215">
       <c r="A215" s="2" t="s">
-        <v>225</v>
+        <v>103</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>225</v>
+        <v>103</v>
       </c>
       <c r="C215" s="2" t="s">
         <v>70</v>
@@ -4124,10 +4373,10 @@
     </row>
     <row r="216">
       <c r="A216" s="2" t="s">
-        <v>226</v>
+        <v>104</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>226</v>
+        <v>104</v>
       </c>
       <c r="C216" s="2" t="s">
         <v>70</v>
@@ -4138,10 +4387,10 @@
     </row>
     <row r="217">
       <c r="A217" s="2" t="s">
-        <v>227</v>
+        <v>105</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>227</v>
+        <v>105</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>70</v>
@@ -4152,27 +4401,27 @@
     </row>
     <row r="218">
       <c r="A218" s="2" t="s">
-        <v>228</v>
+        <v>107</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>228</v>
+        <v>107</v>
       </c>
       <c r="C218" s="2" t="s">
         <v>70</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="s">
-        <v>229</v>
+        <v>149</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>229</v>
+        <v>150</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>70</v>
+        <v>151</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>17</v>
@@ -4180,13 +4429,13 @@
     </row>
     <row r="220">
       <c r="A220" s="2" t="s">
-        <v>230</v>
+        <v>152</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>230</v>
+        <v>153</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>70</v>
+        <v>151</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>17</v>
@@ -4194,13 +4443,13 @@
     </row>
     <row r="221">
       <c r="A221" s="2" t="s">
-        <v>231</v>
+        <v>154</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>231</v>
+        <v>29</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>70</v>
+        <v>151</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>17</v>
@@ -4208,13 +4457,13 @@
     </row>
     <row r="222">
       <c r="A222" s="2" t="s">
-        <v>232</v>
+        <v>155</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>232</v>
+        <v>156</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>70</v>
+        <v>151</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>17</v>
@@ -4222,13 +4471,13 @@
     </row>
     <row r="223">
       <c r="A223" s="2" t="s">
-        <v>233</v>
+        <v>157</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>233</v>
+        <v>158</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>70</v>
+        <v>151</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>17</v>
@@ -4236,13 +4485,13 @@
     </row>
     <row r="224">
       <c r="A224" s="2" t="s">
-        <v>234</v>
+        <v>159</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>234</v>
+        <v>118</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>70</v>
+        <v>151</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>17</v>
@@ -4250,13 +4499,13 @@
     </row>
     <row r="225">
       <c r="A225" s="2" t="s">
-        <v>235</v>
+        <v>160</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>235</v>
+        <v>161</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>70</v>
+        <v>151</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>17</v>
@@ -4264,41 +4513,41 @@
     </row>
     <row r="226">
       <c r="A226" s="2" t="s">
-        <v>236</v>
+        <v>162</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>236</v>
+        <v>163</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>70</v>
+        <v>164</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>237</v>
+        <v>166</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>70</v>
+        <v>164</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="s">
-        <v>238</v>
+        <v>167</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>238</v>
+        <v>150</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
       <c r="D228" s="2" t="s">
         <v>17</v>
@@ -4306,13 +4555,13 @@
     </row>
     <row r="229">
       <c r="A229" s="2" t="s">
-        <v>239</v>
+        <v>169</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>239</v>
+        <v>153</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>17</v>
@@ -4320,13 +4569,13 @@
     </row>
     <row r="230">
       <c r="A230" s="2" t="s">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>240</v>
+        <v>29</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
       <c r="D230" s="2" t="s">
         <v>17</v>
@@ -4334,97 +4583,97 @@
     </row>
     <row r="231">
       <c r="A231" s="2" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>241</v>
+        <v>118</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="s">
-        <v>242</v>
+        <v>172</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>242</v>
+        <v>173</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="s">
-        <v>243</v>
+        <v>174</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>243</v>
+        <v>161</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="s">
-        <v>244</v>
+        <v>175</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>244</v>
+        <v>29</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>70</v>
+        <v>176</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="s">
-        <v>245</v>
+        <v>177</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>245</v>
+        <v>150</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>70</v>
+        <v>178</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="s">
-        <v>246</v>
+        <v>179</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>246</v>
+        <v>153</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>70</v>
+        <v>178</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="s">
-        <v>247</v>
+        <v>180</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>247</v>
+        <v>29</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>70</v>
+        <v>178</v>
       </c>
       <c r="D237" s="2" t="s">
         <v>17</v>
@@ -4432,13 +4681,13 @@
     </row>
     <row r="238">
       <c r="A238" s="2" t="s">
-        <v>248</v>
+        <v>181</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>248</v>
+        <v>156</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>70</v>
+        <v>178</v>
       </c>
       <c r="D238" s="2" t="s">
         <v>17</v>
@@ -4446,13 +4695,13 @@
     </row>
     <row r="239">
       <c r="A239" s="2" t="s">
-        <v>249</v>
+        <v>182</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>249</v>
+        <v>118</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>70</v>
+        <v>178</v>
       </c>
       <c r="D239" s="2" t="s">
         <v>17</v>
@@ -4460,13 +4709,13 @@
     </row>
     <row r="240">
       <c r="A240" s="2" t="s">
-        <v>250</v>
+        <v>183</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>250</v>
+        <v>184</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>70</v>
+        <v>178</v>
       </c>
       <c r="D240" s="2" t="s">
         <v>17</v>
@@ -4474,13 +4723,13 @@
     </row>
     <row r="241">
       <c r="A241" s="2" t="s">
-        <v>251</v>
+        <v>185</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>251</v>
+        <v>161</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>70</v>
+        <v>178</v>
       </c>
       <c r="D241" s="2" t="s">
         <v>17</v>
@@ -4488,13 +4737,13 @@
     </row>
     <row r="242">
       <c r="A242" s="2" t="s">
-        <v>252</v>
+        <v>186</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>252</v>
+        <v>150</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>70</v>
+        <v>187</v>
       </c>
       <c r="D242" s="2" t="s">
         <v>17</v>
@@ -4502,13 +4751,13 @@
     </row>
     <row r="243">
       <c r="A243" s="2" t="s">
-        <v>253</v>
+        <v>188</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>253</v>
+        <v>153</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>70</v>
+        <v>187</v>
       </c>
       <c r="D243" s="2" t="s">
         <v>17</v>
@@ -4516,27 +4765,27 @@
     </row>
     <row r="244">
       <c r="A244" s="2" t="s">
-        <v>254</v>
+        <v>189</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>254</v>
+        <v>29</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>70</v>
+        <v>187</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="s">
-        <v>255</v>
+        <v>190</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>255</v>
+        <v>156</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>70</v>
+        <v>187</v>
       </c>
       <c r="D245" s="2" t="s">
         <v>17</v>
@@ -4544,197 +4793,209 @@
     </row>
     <row r="246">
       <c r="A246" s="2" t="s">
-        <v>256</v>
+        <v>191</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>256</v>
+        <v>118</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>70</v>
+        <v>187</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="B247" s="6"/>
-      <c r="C247" s="6"/>
-      <c r="D247" s="6"/>
+      <c r="A247" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C247" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D247" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="s">
-        <v>6</v>
+        <v>193</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>6</v>
+        <v>161</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>7</v>
+        <v>187</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="s">
-        <v>9</v>
+        <v>194</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>9</v>
+        <v>150</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>7</v>
+        <v>195</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="s">
-        <v>11</v>
+        <v>196</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>11</v>
+        <v>153</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>7</v>
+        <v>195</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="s">
-        <v>13</v>
+        <v>197</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>7</v>
+        <v>195</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="s">
-        <v>14</v>
+        <v>198</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>14</v>
+        <v>156</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>7</v>
+        <v>195</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="B253" s="6"/>
-      <c r="C253" s="6"/>
-      <c r="D253" s="6"/>
+      <c r="A253" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C253" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="s">
-        <v>21</v>
+        <v>201</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>21</v>
+        <v>118</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>22</v>
+        <v>195</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="s">
-        <v>23</v>
+        <v>202</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>23</v>
+        <v>203</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>22</v>
+        <v>195</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="s">
-        <v>24</v>
+        <v>204</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>22</v>
+        <v>205</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="s">
-        <v>25</v>
+        <v>206</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>25</v>
+        <v>153</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>22</v>
+        <v>205</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="s">
-        <v>26</v>
+        <v>207</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>22</v>
+        <v>205</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="s">
-        <v>27</v>
+        <v>208</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>27</v>
+        <v>156</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>22</v>
+        <v>205</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="s">
-        <v>28</v>
+        <v>209</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>28</v>
+        <v>118</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>22</v>
+        <v>205</v>
       </c>
       <c r="D260" s="2" t="s">
         <v>17</v>
@@ -4742,35 +5003,41 @@
     </row>
     <row r="261">
       <c r="A261" s="2" t="s">
-        <v>29</v>
+        <v>210</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>29</v>
+        <v>211</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>22</v>
+        <v>205</v>
       </c>
       <c r="D261" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="B262" s="6"/>
-      <c r="C262" s="6"/>
-      <c r="D262" s="6"/>
+      <c r="A262" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C262" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D262" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="s">
-        <v>29</v>
+        <v>213</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>29</v>
+        <v>161</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>31</v>
+        <v>205</v>
       </c>
       <c r="D263" s="2" t="s">
         <v>17</v>
@@ -4778,13 +5045,13 @@
     </row>
     <row r="264">
       <c r="A264" s="2" t="s">
-        <v>32</v>
+        <v>214</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>32</v>
+        <v>150</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>31</v>
+        <v>215</v>
       </c>
       <c r="D264" s="2" t="s">
         <v>17</v>
@@ -4792,13 +5059,13 @@
     </row>
     <row r="265">
       <c r="A265" s="2" t="s">
-        <v>33</v>
+        <v>216</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>33</v>
+        <v>217</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>31</v>
+        <v>215</v>
       </c>
       <c r="D265" s="2" t="s">
         <v>17</v>
@@ -4806,13 +5073,13 @@
     </row>
     <row r="266">
       <c r="A266" s="2" t="s">
-        <v>34</v>
+        <v>218</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>34</v>
+        <v>153</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>31</v>
+        <v>215</v>
       </c>
       <c r="D266" s="2" t="s">
         <v>17</v>
@@ -4820,13 +5087,13 @@
     </row>
     <row r="267">
       <c r="A267" s="2" t="s">
-        <v>35</v>
+        <v>219</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>31</v>
+        <v>215</v>
       </c>
       <c r="D267" s="2" t="s">
         <v>17</v>
@@ -4834,13 +5101,13 @@
     </row>
     <row r="268">
       <c r="A268" s="2" t="s">
-        <v>36</v>
+        <v>220</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>36</v>
+        <v>156</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>31</v>
+        <v>215</v>
       </c>
       <c r="D268" s="2" t="s">
         <v>17</v>
@@ -4848,13 +5115,13 @@
     </row>
     <row r="269">
       <c r="A269" s="2" t="s">
-        <v>37</v>
+        <v>221</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>37</v>
+        <v>118</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>31</v>
+        <v>215</v>
       </c>
       <c r="D269" s="2" t="s">
         <v>17</v>
@@ -4862,13 +5129,13 @@
     </row>
     <row r="270">
       <c r="A270" s="2" t="s">
-        <v>38</v>
+        <v>222</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>38</v>
+        <v>161</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>31</v>
+        <v>215</v>
       </c>
       <c r="D270" s="2" t="s">
         <v>17</v>
@@ -4876,13 +5143,13 @@
     </row>
     <row r="271">
       <c r="A271" s="2" t="s">
-        <v>39</v>
+        <v>223</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>39</v>
+        <v>150</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>31</v>
+        <v>224</v>
       </c>
       <c r="D271" s="2" t="s">
         <v>17</v>
@@ -4890,13 +5157,13 @@
     </row>
     <row r="272">
       <c r="A272" s="2" t="s">
-        <v>40</v>
+        <v>225</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>40</v>
+        <v>153</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>31</v>
+        <v>224</v>
       </c>
       <c r="D272" s="2" t="s">
         <v>17</v>
@@ -4904,13 +5171,13 @@
     </row>
     <row r="273">
       <c r="A273" s="2" t="s">
-        <v>41</v>
+        <v>226</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>31</v>
+        <v>224</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>17</v>
@@ -4918,13 +5185,13 @@
     </row>
     <row r="274">
       <c r="A274" s="2" t="s">
-        <v>42</v>
+        <v>227</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>42</v>
+        <v>156</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>31</v>
+        <v>224</v>
       </c>
       <c r="D274" s="2" t="s">
         <v>17</v>
@@ -4932,63 +5199,69 @@
     </row>
     <row r="275">
       <c r="A275" s="2" t="s">
-        <v>43</v>
+        <v>228</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>43</v>
+        <v>118</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>31</v>
+        <v>224</v>
       </c>
       <c r="D275" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="B276" s="6"/>
-      <c r="C276" s="6"/>
-      <c r="D276" s="6"/>
+      <c r="A276" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C276" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D276" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="s">
-        <v>6</v>
+        <v>230</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>45</v>
+        <v>231</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="s">
-        <v>46</v>
+        <v>232</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>46</v>
+        <v>153</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>45</v>
+        <v>231</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="s">
-        <v>47</v>
+        <v>233</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>45</v>
+        <v>231</v>
       </c>
       <c r="D279" s="2" t="s">
         <v>17</v>
@@ -4996,91 +5269,97 @@
     </row>
     <row r="280">
       <c r="A280" s="2" t="s">
-        <v>48</v>
+        <v>234</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>48</v>
+        <v>156</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>45</v>
+        <v>231</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="s">
-        <v>50</v>
+        <v>235</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>50</v>
+        <v>236</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>45</v>
+        <v>231</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="B282" s="6"/>
-      <c r="C282" s="6"/>
-      <c r="D282" s="6"/>
+      <c r="A282" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B282" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C282" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D282" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="s">
-        <v>6</v>
+        <v>238</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>6</v>
+        <v>161</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>52</v>
+        <v>231</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="s">
-        <v>53</v>
+        <v>239</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>53</v>
+        <v>150</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>52</v>
+        <v>240</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="s">
-        <v>54</v>
+        <v>241</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>54</v>
+        <v>153</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>52</v>
+        <v>240</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="s">
-        <v>55</v>
+        <v>242</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>52</v>
+        <v>240</v>
       </c>
       <c r="D286" s="2" t="s">
         <v>17</v>
@@ -5088,69 +5367,69 @@
     </row>
     <row r="287">
       <c r="A287" s="2" t="s">
-        <v>56</v>
+        <v>243</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>56</v>
+        <v>156</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>52</v>
+        <v>240</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="s">
-        <v>57</v>
+        <v>244</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>57</v>
+        <v>118</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>52</v>
+        <v>240</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="s">
-        <v>58</v>
+        <v>245</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>58</v>
+        <v>161</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>52</v>
+        <v>240</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="s">
-        <v>59</v>
+        <v>246</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>59</v>
+        <v>150</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>52</v>
+        <v>247</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="s">
-        <v>60</v>
+        <v>248</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>60</v>
+        <v>153</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>52</v>
+        <v>247</v>
       </c>
       <c r="D291" s="2" t="s">
         <v>17</v>
@@ -5158,13 +5437,13 @@
     </row>
     <row r="292">
       <c r="A292" s="2" t="s">
-        <v>61</v>
+        <v>249</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>52</v>
+        <v>247</v>
       </c>
       <c r="D292" s="2" t="s">
         <v>17</v>
@@ -5172,13 +5451,13 @@
     </row>
     <row r="293">
       <c r="A293" s="2" t="s">
-        <v>62</v>
+        <v>250</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>62</v>
+        <v>156</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>52</v>
+        <v>247</v>
       </c>
       <c r="D293" s="2" t="s">
         <v>17</v>
@@ -5186,13 +5465,13 @@
     </row>
     <row r="294">
       <c r="A294" s="2" t="s">
-        <v>63</v>
+        <v>251</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>63</v>
+        <v>118</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>52</v>
+        <v>247</v>
       </c>
       <c r="D294" s="2" t="s">
         <v>17</v>
@@ -5200,77 +5479,83 @@
     </row>
     <row r="295">
       <c r="A295" s="2" t="s">
-        <v>64</v>
+        <v>252</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>64</v>
+        <v>161</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>52</v>
+        <v>247</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="s">
-        <v>65</v>
+        <v>253</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>52</v>
+        <v>254</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="s">
-        <v>66</v>
+        <v>255</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>66</v>
+        <v>153</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>52</v>
+        <v>254</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="s">
-        <v>67</v>
+        <v>256</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>52</v>
+        <v>254</v>
       </c>
       <c r="D298" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="B299" s="6"/>
-      <c r="C299" s="6"/>
-      <c r="D299" s="6"/>
+      <c r="A299" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B299" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C299" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D299" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="s">
-        <v>43</v>
+        <v>258</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>43</v>
+        <v>118</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>70</v>
+        <v>254</v>
       </c>
       <c r="D300" s="2" t="s">
         <v>17</v>
@@ -5278,13 +5563,13 @@
     </row>
     <row r="301">
       <c r="A301" s="2" t="s">
-        <v>72</v>
+        <v>259</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>72</v>
+        <v>161</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>70</v>
+        <v>254</v>
       </c>
       <c r="D301" s="2" t="s">
         <v>17</v>
@@ -5292,13 +5577,13 @@
     </row>
     <row r="302">
       <c r="A302" s="2" t="s">
-        <v>73</v>
+        <v>260</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>70</v>
+        <v>261</v>
       </c>
       <c r="D302" s="2" t="s">
         <v>17</v>
@@ -5306,13 +5591,13 @@
     </row>
     <row r="303">
       <c r="A303" s="2" t="s">
-        <v>74</v>
+        <v>262</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>74</v>
+        <v>153</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>70</v>
+        <v>261</v>
       </c>
       <c r="D303" s="2" t="s">
         <v>17</v>
@@ -5320,13 +5605,13 @@
     </row>
     <row r="304">
       <c r="A304" s="2" t="s">
-        <v>75</v>
+        <v>263</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>70</v>
+        <v>261</v>
       </c>
       <c r="D304" s="2" t="s">
         <v>17</v>
@@ -5334,13 +5619,13 @@
     </row>
     <row r="305">
       <c r="A305" s="2" t="s">
-        <v>76</v>
+        <v>264</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>76</v>
+        <v>156</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>70</v>
+        <v>261</v>
       </c>
       <c r="D305" s="2" t="s">
         <v>17</v>
@@ -5348,13 +5633,13 @@
     </row>
     <row r="306">
       <c r="A306" s="2" t="s">
-        <v>77</v>
+        <v>265</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>70</v>
+        <v>261</v>
       </c>
       <c r="D306" s="2" t="s">
         <v>17</v>
@@ -5362,13 +5647,13 @@
     </row>
     <row r="307">
       <c r="A307" s="2" t="s">
-        <v>78</v>
+        <v>266</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>78</v>
+        <v>161</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>70</v>
+        <v>261</v>
       </c>
       <c r="D307" s="2" t="s">
         <v>17</v>
@@ -5376,13 +5661,13 @@
     </row>
     <row r="308">
       <c r="A308" s="2" t="s">
-        <v>79</v>
+        <v>267</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>70</v>
+        <v>268</v>
       </c>
       <c r="D308" s="2" t="s">
         <v>17</v>
@@ -5390,13 +5675,13 @@
     </row>
     <row r="309">
       <c r="A309" s="2" t="s">
-        <v>80</v>
+        <v>269</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>70</v>
+        <v>268</v>
       </c>
       <c r="D309" s="2" t="s">
         <v>17</v>
@@ -5404,13 +5689,13 @@
     </row>
     <row r="310">
       <c r="A310" s="2" t="s">
-        <v>81</v>
+        <v>270</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>70</v>
+        <v>268</v>
       </c>
       <c r="D310" s="2" t="s">
         <v>17</v>
@@ -5418,13 +5703,13 @@
     </row>
     <row r="311">
       <c r="A311" s="2" t="s">
-        <v>82</v>
+        <v>271</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>70</v>
+        <v>268</v>
       </c>
       <c r="D311" s="2" t="s">
         <v>17</v>
@@ -5432,13 +5717,13 @@
     </row>
     <row r="312">
       <c r="A312" s="2" t="s">
-        <v>83</v>
+        <v>272</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>70</v>
+        <v>268</v>
       </c>
       <c r="D312" s="2" t="s">
         <v>17</v>
@@ -5446,13 +5731,13 @@
     </row>
     <row r="313">
       <c r="A313" s="2" t="s">
-        <v>84</v>
+        <v>273</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>84</v>
+        <v>161</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>70</v>
+        <v>268</v>
       </c>
       <c r="D313" s="2" t="s">
         <v>17</v>
@@ -5460,13 +5745,13 @@
     </row>
     <row r="314">
       <c r="A314" s="2" t="s">
-        <v>85</v>
+        <v>274</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>70</v>
+        <v>275</v>
       </c>
       <c r="D314" s="2" t="s">
         <v>17</v>
@@ -5474,13 +5759,13 @@
     </row>
     <row r="315">
       <c r="A315" s="2" t="s">
-        <v>86</v>
+        <v>276</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>86</v>
+        <v>153</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>70</v>
+        <v>275</v>
       </c>
       <c r="D315" s="2" t="s">
         <v>17</v>
@@ -5488,13 +5773,13 @@
     </row>
     <row r="316">
       <c r="A316" s="2" t="s">
-        <v>88</v>
+        <v>277</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>70</v>
+        <v>275</v>
       </c>
       <c r="D316" s="2" t="s">
         <v>17</v>
@@ -5502,13 +5787,13 @@
     </row>
     <row r="317">
       <c r="A317" s="2" t="s">
-        <v>89</v>
+        <v>278</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>89</v>
+        <v>156</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>70</v>
+        <v>275</v>
       </c>
       <c r="D317" s="2" t="s">
         <v>17</v>
@@ -5516,13 +5801,13 @@
     </row>
     <row r="318">
       <c r="A318" s="2" t="s">
-        <v>90</v>
+        <v>279</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>70</v>
+        <v>275</v>
       </c>
       <c r="D318" s="2" t="s">
         <v>17</v>
@@ -5530,13 +5815,13 @@
     </row>
     <row r="319">
       <c r="A319" s="2" t="s">
-        <v>91</v>
+        <v>280</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>91</v>
+        <v>161</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>70</v>
+        <v>275</v>
       </c>
       <c r="D319" s="2" t="s">
         <v>17</v>
@@ -5544,97 +5829,97 @@
     </row>
     <row r="320">
       <c r="A320" s="2" t="s">
-        <v>92</v>
+        <v>281</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>92</v>
+        <v>166</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>70</v>
+        <v>275</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="s">
-        <v>93</v>
+        <v>282</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>93</v>
+        <v>283</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>70</v>
+        <v>284</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="s">
-        <v>95</v>
+        <v>285</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>95</v>
+        <v>286</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>70</v>
+        <v>287</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="s">
-        <v>96</v>
+        <v>288</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>96</v>
+        <v>289</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>70</v>
+        <v>290</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="s">
-        <v>97</v>
+        <v>291</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>97</v>
+        <v>289</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>70</v>
+        <v>292</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="s">
-        <v>99</v>
+        <v>293</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>99</v>
+        <v>294</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>70</v>
+        <v>292</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="s">
-        <v>100</v>
+        <v>295</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>100</v>
+        <v>296</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>70</v>
+        <v>297</v>
       </c>
       <c r="D326" s="2" t="s">
         <v>17</v>
@@ -5642,13 +5927,13 @@
     </row>
     <row r="327">
       <c r="A327" s="2" t="s">
-        <v>101</v>
+        <v>298</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>101</v>
+        <v>299</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>70</v>
+        <v>297</v>
       </c>
       <c r="D327" s="2" t="s">
         <v>17</v>
@@ -5656,13 +5941,13 @@
     </row>
     <row r="328">
       <c r="A328" s="2" t="s">
-        <v>102</v>
+        <v>300</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>102</v>
+        <v>301</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>70</v>
+        <v>302</v>
       </c>
       <c r="D328" s="2" t="s">
         <v>17</v>
@@ -5670,13 +5955,13 @@
     </row>
     <row r="329">
       <c r="A329" s="2" t="s">
-        <v>103</v>
+        <v>303</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>70</v>
+        <v>302</v>
       </c>
       <c r="D329" s="2" t="s">
         <v>17</v>
@@ -5684,27 +5969,27 @@
     </row>
     <row r="330">
       <c r="A330" s="2" t="s">
-        <v>104</v>
+        <v>304</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>104</v>
+        <v>305</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>70</v>
+        <v>302</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="s">
-        <v>105</v>
+        <v>306</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>105</v>
+        <v>142</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>70</v>
+        <v>302</v>
       </c>
       <c r="D331" s="2" t="s">
         <v>17</v>
@@ -5712,13 +5997,13 @@
     </row>
     <row r="332">
       <c r="A332" s="2" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>107</v>
+        <v>283</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>70</v>
+        <v>308</v>
       </c>
       <c r="D332" s="2" t="s">
         <v>10</v>
@@ -5726,7 +6011,7 @@
     </row>
     <row r="333">
       <c r="A333" s="6" t="s">
-        <v>263</v>
+        <v>309</v>
       </c>
       <c r="B333" s="6"/>
       <c r="C333" s="6"/>
@@ -5743,7 +6028,7 @@
         <v>6</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>264</v>
+        <v>310</v>
       </c>
     </row>
     <row r="335">
@@ -5757,7 +6042,7 @@
         <v>6</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>264</v>
+        <v>310</v>
       </c>
     </row>
     <row r="336">
@@ -5771,7 +6056,7 @@
         <v>6</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>264</v>
+        <v>310</v>
       </c>
     </row>
     <row r="337">
@@ -5785,7 +6070,7 @@
         <v>6</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>264</v>
+        <v>310</v>
       </c>
     </row>
     <row r="338">
@@ -5799,7 +6084,7 @@
         <v>6</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>264</v>
+        <v>310</v>
       </c>
     </row>
     <row r="339">
@@ -5813,144 +6098,2626 @@
         <v>6</v>
       </c>
       <c r="D339" s="2" t="s">
-        <v>264</v>
+        <v>310</v>
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="B340" s="6"/>
-      <c r="C340" s="6"/>
-      <c r="D340" s="6"/>
+      <c r="A340" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B340" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C340" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D340" s="2" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="s">
-        <v>7</v>
+        <v>312</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="C341" s="2"/>
-      <c r="D341" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="C341" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D341" s="2" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="s">
-        <v>22</v>
+        <v>313</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="C342" s="2"/>
-      <c r="D342" s="2"/>
+        <v>313</v>
+      </c>
+      <c r="C342" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D342" s="2" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="s">
-        <v>110</v>
+        <v>314</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="C343" s="2"/>
-      <c r="D343" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="C343" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D343" s="2" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="s">
-        <v>70</v>
+        <v>315</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="C344" s="2"/>
-      <c r="D344" s="2"/>
+        <v>315</v>
+      </c>
+      <c r="C344" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D344" s="2" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="s">
-        <v>31</v>
+        <v>164</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="C345" s="2"/>
-      <c r="D345" s="2"/>
+        <v>164</v>
+      </c>
+      <c r="C345" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D345" s="2" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="s">
-        <v>45</v>
+        <v>168</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="C346" s="2"/>
-      <c r="D346" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="C346" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D346" s="2" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="347">
-      <c r="A347" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="B347" s="6"/>
-      <c r="C347" s="6"/>
-      <c r="D347" s="6"/>
+      <c r="A347" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B347" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C347" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D347" s="2" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="s">
-        <v>7</v>
+        <v>317</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C348" s="2"/>
-      <c r="D348" s="2"/>
+        <v>317</v>
+      </c>
+      <c r="C348" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D348" s="2" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="s">
-        <v>22</v>
+        <v>176</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C349" s="2"/>
-      <c r="D349" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="C349" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D349" s="2" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="s">
-        <v>31</v>
+        <v>318</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C350" s="2"/>
-      <c r="D350" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="C350" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D350" s="2" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="s">
-        <v>45</v>
+        <v>319</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C351" s="2"/>
-      <c r="D351" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="C351" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D351" s="2" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="s">
-        <v>70</v>
+        <v>320</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C352" s="2"/>
-      <c r="D352" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="C352" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D352" s="2" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B353" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C353" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D353" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B354" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C354" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D354" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B355" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C355" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D355" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B356" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C356" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D356" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B357" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C357" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D357" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B358" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C358" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D358" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B359" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C359" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D359" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B360" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C360" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D360" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B361" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C361" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D361" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B362" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C362" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D362" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B363" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C363" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D363" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B364" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C364" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D364" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B365" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="C365" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D365" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B366" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C366" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D366" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B367" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C367" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D367" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B368" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C368" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D368" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="B369" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C369" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D369" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B370" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C370" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D370" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B371" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="C371" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D371" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B372" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C372" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D372" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B373" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C373" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D373" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B374" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C374" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D374" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B375" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C375" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D375" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B376" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C376" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D376" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B377" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C377" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D377" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B378" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="C378" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D378" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B379" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="C379" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D379" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B380" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="C380" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D380" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B381" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C381" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D381" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B382" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C382" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D382" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B383" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C383" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D383" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B384" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C384" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D384" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B385" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C385" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D385" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B386" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C386" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D386" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B387" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C387" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D387" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B388" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C388" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D388" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B389" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C389" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D389" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B390" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C390" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D390" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B391" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C391" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D391" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B392" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C392" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D392" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B393" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C393" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D393" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B394" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C394" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D394" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B395" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C395" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D395" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B396" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C396" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D396" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B397" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C397" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D397" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B398" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C398" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D398" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B399" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="C399" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D399" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B400" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C400" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D400" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B401" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C401" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D401" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B402" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="C402" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D402" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B403" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C403" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D403" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B404" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C404" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D404" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B405" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="C405" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D405" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B406" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C406" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D406" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B407" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="C407" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D407" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B408" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C408" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D408" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B409" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="C409" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D409" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B410" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C410" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D410" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B411" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C411" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D411" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B412" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C412" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D412" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="B413" s="6"/>
+      <c r="C413" s="6"/>
+      <c r="D413" s="6"/>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B414" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C414" s="2"/>
+      <c r="D414" s="2"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B415" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C415" s="2"/>
+      <c r="D415" s="2"/>
+    </row>
+    <row r="416">
+      <c r="A416" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B353" s="2" t="s">
+      <c r="B416" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C416" s="2"/>
+      <c r="D416" s="2"/>
+    </row>
+    <row r="417">
+      <c r="A417" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B417" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C417" s="2"/>
+      <c r="D417" s="2"/>
+    </row>
+    <row r="418">
+      <c r="A418" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B418" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C418" s="2"/>
+      <c r="D418" s="2"/>
+    </row>
+    <row r="419">
+      <c r="A419" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B419" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C419" s="2"/>
+      <c r="D419" s="2"/>
+    </row>
+    <row r="420">
+      <c r="A420" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B420" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C420" s="2"/>
+      <c r="D420" s="2"/>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B421" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C421" s="2"/>
+      <c r="D421" s="2"/>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B422" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C422" s="2"/>
+      <c r="D422" s="2"/>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B423" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C423" s="2"/>
+      <c r="D423" s="2"/>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B424" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C424" s="2"/>
+      <c r="D424" s="2"/>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B425" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C425" s="2"/>
+      <c r="D425" s="2"/>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B426" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C426" s="2"/>
+      <c r="D426" s="2"/>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B427" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C427" s="2"/>
+      <c r="D427" s="2"/>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B428" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C428" s="2"/>
+      <c r="D428" s="2"/>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B429" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C429" s="2"/>
+      <c r="D429" s="2"/>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B430" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C430" s="2"/>
+      <c r="D430" s="2"/>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B431" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C431" s="2"/>
+      <c r="D431" s="2"/>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B432" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C432" s="2"/>
+      <c r="D432" s="2"/>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B433" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C433" s="2"/>
+      <c r="D433" s="2"/>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B434" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C434" s="2"/>
+      <c r="D434" s="2"/>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B435" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C435" s="2"/>
+      <c r="D435" s="2"/>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B436" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C436" s="2"/>
+      <c r="D436" s="2"/>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B437" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C437" s="2"/>
+      <c r="D437" s="2"/>
+    </row>
+    <row r="438">
+      <c r="A438" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B438" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C438" s="2"/>
+      <c r="D438" s="2"/>
+    </row>
+    <row r="439">
+      <c r="A439" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B439" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C439" s="2"/>
+      <c r="D439" s="2"/>
+    </row>
+    <row r="440">
+      <c r="A440" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B440" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C440" s="2"/>
+      <c r="D440" s="2"/>
+    </row>
+    <row r="441">
+      <c r="A441" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B441" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C441" s="2"/>
+      <c r="D441" s="2"/>
+    </row>
+    <row r="442">
+      <c r="A442" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B442" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C442" s="2"/>
+      <c r="D442" s="2"/>
+    </row>
+    <row r="443">
+      <c r="A443" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B443" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C443" s="2"/>
+      <c r="D443" s="2"/>
+    </row>
+    <row r="444">
+      <c r="A444" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B444" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C444" s="2"/>
+      <c r="D444" s="2"/>
+    </row>
+    <row r="445">
+      <c r="A445" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B445" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C445" s="2"/>
+      <c r="D445" s="2"/>
+    </row>
+    <row r="446">
+      <c r="A446" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B446" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C446" s="2"/>
+      <c r="D446" s="2"/>
+    </row>
+    <row r="447">
+      <c r="A447" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B447" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C447" s="2"/>
+      <c r="D447" s="2"/>
+    </row>
+    <row r="448">
+      <c r="A448" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B448" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C448" s="2"/>
+      <c r="D448" s="2"/>
+    </row>
+    <row r="449">
+      <c r="A449" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="B449" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C449" s="2"/>
+      <c r="D449" s="2"/>
+    </row>
+    <row r="450">
+      <c r="A450" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B450" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C450" s="2"/>
+      <c r="D450" s="2"/>
+    </row>
+    <row r="451">
+      <c r="A451" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B451" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C451" s="2"/>
+      <c r="D451" s="2"/>
+    </row>
+    <row r="452">
+      <c r="A452" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B452" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C452" s="2"/>
+      <c r="D452" s="2"/>
+    </row>
+    <row r="453">
+      <c r="A453" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B453" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C453" s="2"/>
+      <c r="D453" s="2"/>
+    </row>
+    <row r="454">
+      <c r="A454" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="C353" s="2"/>
-      <c r="D353" s="2"/>
+      <c r="B454" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C454" s="2"/>
+      <c r="D454" s="2"/>
+    </row>
+    <row r="455">
+      <c r="A455" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B455" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C455" s="2"/>
+      <c r="D455" s="2"/>
+    </row>
+    <row r="456">
+      <c r="A456" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B456" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C456" s="2"/>
+      <c r="D456" s="2"/>
+    </row>
+    <row r="457">
+      <c r="A457" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B457" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C457" s="2"/>
+      <c r="D457" s="2"/>
+    </row>
+    <row r="458">
+      <c r="A458" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B458" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C458" s="2"/>
+      <c r="D458" s="2"/>
+    </row>
+    <row r="459">
+      <c r="A459" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B459" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C459" s="2"/>
+      <c r="D459" s="2"/>
+    </row>
+    <row r="460">
+      <c r="A460" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B460" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C460" s="2"/>
+      <c r="D460" s="2"/>
+    </row>
+    <row r="461">
+      <c r="A461" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B461" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C461" s="2"/>
+      <c r="D461" s="2"/>
+    </row>
+    <row r="462">
+      <c r="A462" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B462" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C462" s="2"/>
+      <c r="D462" s="2"/>
+    </row>
+    <row r="463">
+      <c r="A463" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B463" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C463" s="2"/>
+      <c r="D463" s="2"/>
+    </row>
+    <row r="464">
+      <c r="A464" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B464" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C464" s="2"/>
+      <c r="D464" s="2"/>
+    </row>
+    <row r="465">
+      <c r="A465" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B465" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C465" s="2"/>
+      <c r="D465" s="2"/>
+    </row>
+    <row r="466">
+      <c r="A466" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B466" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C466" s="2"/>
+      <c r="D466" s="2"/>
+    </row>
+    <row r="467">
+      <c r="A467" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B467" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C467" s="2"/>
+      <c r="D467" s="2"/>
+    </row>
+    <row r="468">
+      <c r="A468" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B468" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C468" s="2"/>
+      <c r="D468" s="2"/>
+    </row>
+    <row r="469">
+      <c r="A469" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B469" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C469" s="2"/>
+      <c r="D469" s="2"/>
+    </row>
+    <row r="470">
+      <c r="A470" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B470" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C470" s="2"/>
+      <c r="D470" s="2"/>
+    </row>
+    <row r="471">
+      <c r="A471" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B471" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C471" s="2"/>
+      <c r="D471" s="2"/>
+    </row>
+    <row r="472">
+      <c r="A472" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B472" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C472" s="2"/>
+      <c r="D472" s="2"/>
+    </row>
+    <row r="473">
+      <c r="A473" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B473" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C473" s="2"/>
+      <c r="D473" s="2"/>
+    </row>
+    <row r="474">
+      <c r="A474" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B474" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C474" s="2"/>
+      <c r="D474" s="2"/>
+    </row>
+    <row r="475">
+      <c r="A475" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B475" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C475" s="2"/>
+      <c r="D475" s="2"/>
+    </row>
+    <row r="476">
+      <c r="A476" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B476" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C476" s="2"/>
+      <c r="D476" s="2"/>
+    </row>
+    <row r="477">
+      <c r="A477" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B477" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C477" s="2"/>
+      <c r="D477" s="2"/>
+    </row>
+    <row r="478">
+      <c r="A478" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B478" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C478" s="2"/>
+      <c r="D478" s="2"/>
+    </row>
+    <row r="479">
+      <c r="A479" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B479" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C479" s="2"/>
+      <c r="D479" s="2"/>
+    </row>
+    <row r="480">
+      <c r="A480" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B480" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C480" s="2"/>
+      <c r="D480" s="2"/>
+    </row>
+    <row r="481">
+      <c r="A481" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B481" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C481" s="2"/>
+      <c r="D481" s="2"/>
+    </row>
+    <row r="482">
+      <c r="A482" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B482" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C482" s="2"/>
+      <c r="D482" s="2"/>
+    </row>
+    <row r="483">
+      <c r="A483" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B483" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C483" s="2"/>
+      <c r="D483" s="2"/>
+    </row>
+    <row r="484">
+      <c r="A484" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B484" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C484" s="2"/>
+      <c r="D484" s="2"/>
+    </row>
+    <row r="485">
+      <c r="A485" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B485" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C485" s="2"/>
+      <c r="D485" s="2"/>
+    </row>
+    <row r="486">
+      <c r="A486" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B486" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C486" s="2"/>
+      <c r="D486" s="2"/>
+    </row>
+    <row r="487">
+      <c r="A487" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B487" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C487" s="2"/>
+      <c r="D487" s="2"/>
+    </row>
+    <row r="488">
+      <c r="A488" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B488" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C488" s="2"/>
+      <c r="D488" s="2"/>
+    </row>
+    <row r="489">
+      <c r="A489" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B489" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C489" s="2"/>
+      <c r="D489" s="2"/>
+    </row>
+    <row r="490">
+      <c r="A490" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B490" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C490" s="2"/>
+      <c r="D490" s="2"/>
+    </row>
+    <row r="491">
+      <c r="A491" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B491" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C491" s="2"/>
+      <c r="D491" s="2"/>
+    </row>
+    <row r="492">
+      <c r="A492" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B492" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C492" s="2"/>
+      <c r="D492" s="2"/>
+    </row>
+    <row r="493">
+      <c r="A493" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="B493" s="6"/>
+      <c r="C493" s="6"/>
+      <c r="D493" s="6"/>
+    </row>
+    <row r="494">
+      <c r="A494" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B494" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C494" s="2"/>
+      <c r="D494" s="2"/>
+    </row>
+    <row r="495">
+      <c r="A495" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B495" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C495" s="2"/>
+      <c r="D495" s="2"/>
+    </row>
+    <row r="496">
+      <c r="A496" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B496" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C496" s="2"/>
+      <c r="D496" s="2"/>
+    </row>
+    <row r="497">
+      <c r="A497" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B497" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C497" s="2"/>
+      <c r="D497" s="2"/>
+    </row>
+    <row r="498">
+      <c r="A498" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B498" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C498" s="2"/>
+      <c r="D498" s="2"/>
+    </row>
+    <row r="499">
+      <c r="A499" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B499" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C499" s="2"/>
+      <c r="D499" s="2"/>
+    </row>
+    <row r="500">
+      <c r="A500" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B500" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C500" s="2"/>
+      <c r="D500" s="2"/>
+    </row>
+    <row r="501">
+      <c r="A501" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B501" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C501" s="2"/>
+      <c r="D501" s="2"/>
+    </row>
+    <row r="502">
+      <c r="A502" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B502" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C502" s="2"/>
+      <c r="D502" s="2"/>
+    </row>
+    <row r="503">
+      <c r="A503" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B503" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C503" s="2"/>
+      <c r="D503" s="2"/>
+    </row>
+    <row r="504">
+      <c r="A504" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B504" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C504" s="2"/>
+      <c r="D504" s="2"/>
+    </row>
+    <row r="505">
+      <c r="A505" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B505" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C505" s="2"/>
+      <c r="D505" s="2"/>
+    </row>
+    <row r="506">
+      <c r="A506" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B506" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C506" s="2"/>
+      <c r="D506" s="2"/>
+    </row>
+    <row r="507">
+      <c r="A507" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B507" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C507" s="2"/>
+      <c r="D507" s="2"/>
+    </row>
+    <row r="508">
+      <c r="A508" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B508" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C508" s="2"/>
+      <c r="D508" s="2"/>
+    </row>
+    <row r="509">
+      <c r="A509" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B509" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C509" s="2"/>
+      <c r="D509" s="2"/>
+    </row>
+    <row r="510">
+      <c r="A510" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B510" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C510" s="2"/>
+      <c r="D510" s="2"/>
+    </row>
+    <row r="511">
+      <c r="A511" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B511" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C511" s="2"/>
+      <c r="D511" s="2"/>
+    </row>
+    <row r="512">
+      <c r="A512" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B512" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C512" s="2"/>
+      <c r="D512" s="2"/>
+    </row>
+    <row r="513">
+      <c r="A513" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B513" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C513" s="2"/>
+      <c r="D513" s="2"/>
+    </row>
+    <row r="514">
+      <c r="A514" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B514" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C514" s="2"/>
+      <c r="D514" s="2"/>
+    </row>
+    <row r="515">
+      <c r="A515" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B515" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C515" s="2"/>
+      <c r="D515" s="2"/>
+    </row>
+    <row r="516">
+      <c r="A516" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B516" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C516" s="2"/>
+      <c r="D516" s="2"/>
+    </row>
+    <row r="517">
+      <c r="A517" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B517" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C517" s="2"/>
+      <c r="D517" s="2"/>
+    </row>
+    <row r="518">
+      <c r="A518" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B518" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C518" s="2"/>
+      <c r="D518" s="2"/>
+    </row>
+    <row r="519">
+      <c r="A519" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B519" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C519" s="2"/>
+      <c r="D519" s="2"/>
+    </row>
+    <row r="520">
+      <c r="A520" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B520" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C520" s="2"/>
+      <c r="D520" s="2"/>
+    </row>
+    <row r="521">
+      <c r="A521" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B521" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C521" s="2"/>
+      <c r="D521" s="2"/>
+    </row>
+    <row r="522">
+      <c r="A522" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B522" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C522" s="2"/>
+      <c r="D522" s="2"/>
+    </row>
+    <row r="523">
+      <c r="A523" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B523" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C523" s="2"/>
+      <c r="D523" s="2"/>
+    </row>
+    <row r="524">
+      <c r="A524" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B524" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C524" s="2"/>
+      <c r="D524" s="2"/>
+    </row>
+    <row r="525">
+      <c r="A525" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B525" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C525" s="2"/>
+      <c r="D525" s="2"/>
+    </row>
+    <row r="526">
+      <c r="A526" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B526" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C526" s="2"/>
+      <c r="D526" s="2"/>
+    </row>
+    <row r="527">
+      <c r="A527" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B527" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C527" s="2"/>
+      <c r="D527" s="2"/>
+    </row>
+    <row r="528">
+      <c r="A528" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B528" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C528" s="2"/>
+      <c r="D528" s="2"/>
+    </row>
+    <row r="529">
+      <c r="A529" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="B529" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C529" s="2"/>
+      <c r="D529" s="2"/>
+    </row>
+    <row r="530">
+      <c r="A530" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B530" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C530" s="2"/>
+      <c r="D530" s="2"/>
+    </row>
+    <row r="531">
+      <c r="A531" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B531" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C531" s="2"/>
+      <c r="D531" s="2"/>
+    </row>
+    <row r="532">
+      <c r="A532" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B532" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C532" s="2"/>
+      <c r="D532" s="2"/>
+    </row>
+    <row r="533">
+      <c r="A533" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B533" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C533" s="2"/>
+      <c r="D533" s="2"/>
+    </row>
+    <row r="534">
+      <c r="A534" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B534" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C534" s="2"/>
+      <c r="D534" s="2"/>
+    </row>
+    <row r="535">
+      <c r="A535" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B535" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C535" s="2"/>
+      <c r="D535" s="2"/>
+    </row>
+    <row r="536">
+      <c r="A536" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B536" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C536" s="2"/>
+      <c r="D536" s="2"/>
+    </row>
+    <row r="537">
+      <c r="A537" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B537" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C537" s="2"/>
+      <c r="D537" s="2"/>
+    </row>
+    <row r="538">
+      <c r="A538" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B538" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C538" s="2"/>
+      <c r="D538" s="2"/>
+    </row>
+    <row r="539">
+      <c r="A539" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B539" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C539" s="2"/>
+      <c r="D539" s="2"/>
+    </row>
+    <row r="540">
+      <c r="A540" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B540" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C540" s="2"/>
+      <c r="D540" s="2"/>
+    </row>
+    <row r="541">
+      <c r="A541" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B541" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C541" s="2"/>
+      <c r="D541" s="2"/>
+    </row>
+    <row r="542">
+      <c r="A542" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B542" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C542" s="2"/>
+      <c r="D542" s="2"/>
+    </row>
+    <row r="543">
+      <c r="A543" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B543" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C543" s="2"/>
+      <c r="D543" s="2"/>
+    </row>
+    <row r="544">
+      <c r="A544" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B544" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C544" s="2"/>
+      <c r="D544" s="2"/>
+    </row>
+    <row r="545">
+      <c r="A545" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B545" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C545" s="2"/>
+      <c r="D545" s="2"/>
+    </row>
+    <row r="546">
+      <c r="A546" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B546" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C546" s="2"/>
+      <c r="D546" s="2"/>
+    </row>
+    <row r="547">
+      <c r="A547" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B547" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C547" s="2"/>
+      <c r="D547" s="2"/>
+    </row>
+    <row r="548">
+      <c r="A548" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B548" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C548" s="2"/>
+      <c r="D548" s="2"/>
+    </row>
+    <row r="549">
+      <c r="A549" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B549" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C549" s="2"/>
+      <c r="D549" s="2"/>
+    </row>
+    <row r="550">
+      <c r="A550" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B550" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C550" s="2"/>
+      <c r="D550" s="2"/>
+    </row>
+    <row r="551">
+      <c r="A551" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B551" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C551" s="2"/>
+      <c r="D551" s="2"/>
+    </row>
+    <row r="552">
+      <c r="A552" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B552" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C552" s="2"/>
+      <c r="D552" s="2"/>
+    </row>
+    <row r="553">
+      <c r="A553" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B553" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C553" s="2"/>
+      <c r="D553" s="2"/>
+    </row>
+    <row r="554">
+      <c r="A554" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B554" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C554" s="2"/>
+      <c r="D554" s="2"/>
+    </row>
+    <row r="555">
+      <c r="A555" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B555" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C555" s="2"/>
+      <c r="D555" s="2"/>
+    </row>
+    <row r="556">
+      <c r="A556" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B556" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C556" s="2"/>
+      <c r="D556" s="2"/>
+    </row>
+    <row r="557">
+      <c r="A557" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B557" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C557" s="2"/>
+      <c r="D557" s="2"/>
+    </row>
+    <row r="558">
+      <c r="A558" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B558" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C558" s="2"/>
+      <c r="D558" s="2"/>
+    </row>
+    <row r="559">
+      <c r="A559" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B559" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C559" s="2"/>
+      <c r="D559" s="2"/>
+    </row>
+    <row r="560">
+      <c r="A560" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B560" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C560" s="2"/>
+      <c r="D560" s="2"/>
+    </row>
+    <row r="561">
+      <c r="A561" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B561" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C561" s="2"/>
+      <c r="D561" s="2"/>
+    </row>
+    <row r="562">
+      <c r="A562" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B562" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C562" s="2"/>
+      <c r="D562" s="2"/>
+    </row>
+    <row r="563">
+      <c r="A563" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B563" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C563" s="2"/>
+      <c r="D563" s="2"/>
+    </row>
+    <row r="564">
+      <c r="A564" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B564" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C564" s="2"/>
+      <c r="D564" s="2"/>
+    </row>
+    <row r="565">
+      <c r="A565" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B565" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C565" s="2"/>
+      <c r="D565" s="2"/>
+    </row>
+    <row r="566">
+      <c r="A566" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B566" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C566" s="2"/>
+      <c r="D566" s="2"/>
+    </row>
+    <row r="567">
+      <c r="A567" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B567" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C567" s="2"/>
+      <c r="D567" s="2"/>
+    </row>
+    <row r="568">
+      <c r="A568" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B568" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C568" s="2"/>
+      <c r="D568" s="2"/>
+    </row>
+    <row r="569">
+      <c r="A569" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B569" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C569" s="2"/>
+      <c r="D569" s="2"/>
+    </row>
+    <row r="570">
+      <c r="A570" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B570" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C570" s="2"/>
+      <c r="D570" s="2"/>
+    </row>
+    <row r="571">
+      <c r="A571" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B571" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C571" s="2"/>
+      <c r="D571" s="2"/>
+    </row>
+    <row r="572">
+      <c r="A572" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B572" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C572" s="2"/>
+      <c r="D572" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
